--- a/nriss-patch-1/ig/ValueSet-TypeCarteVS.xlsx
+++ b/nriss-patch-1/ig/ValueSet-TypeCarteVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T16:02:13+00:00</t>
+    <t>2026-07-03T07:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
